--- a/Models/Яйца/results/Яйца - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/Яйца/results/Яйца - Результаты прогнозов ХВ средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4310.41</v>
+        <v>2688.42</v>
       </c>
       <c r="C2" t="n">
-        <v>3781.74</v>
+        <v>2369.14</v>
       </c>
       <c r="D2" t="n">
-        <v>6.27</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1190.36</v>
+        <v>1374.14</v>
       </c>
       <c r="C3" t="n">
-        <v>1068.68</v>
+        <v>1272.95</v>
       </c>
       <c r="D3" t="n">
-        <v>5.93</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3728.68</v>
+        <v>4632.18</v>
       </c>
       <c r="C4" t="n">
-        <v>3296.67</v>
+        <v>4041.75</v>
       </c>
       <c r="D4" t="n">
-        <v>7.25</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>569.8</v>
+        <v>536.35</v>
       </c>
       <c r="C5" t="n">
-        <v>519.3</v>
+        <v>503.07</v>
       </c>
       <c r="D5" t="n">
-        <v>18.92</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>271.45</v>
+        <v>340.97</v>
       </c>
       <c r="C6" t="n">
-        <v>244.39</v>
+        <v>301.33</v>
       </c>
       <c r="D6" t="n">
-        <v>4.91</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.51</v>
+        <v>1.89</v>
       </c>
       <c r="C7" t="n">
-        <v>3.06</v>
+        <v>1.71</v>
       </c>
       <c r="D7" t="n">
-        <v>19.22</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="C8" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="D8" t="n">
-        <v>144.4</v>
+        <v>138.61</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1063.23</v>
+        <v>1959.45</v>
       </c>
       <c r="C9" t="n">
-        <v>896.09</v>
+        <v>1695.09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.94</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2032.78</v>
+        <v>1153</v>
       </c>
       <c r="C10" t="n">
-        <v>1861.03</v>
+        <v>1059.44</v>
       </c>
       <c r="D10" t="n">
-        <v>17.52</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>936.54</v>
+        <v>946.96</v>
       </c>
       <c r="C11" t="n">
-        <v>856.49</v>
+        <v>821.46</v>
       </c>
       <c r="D11" t="n">
-        <v>6.87</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2781.87</v>
+        <v>3859.95</v>
       </c>
       <c r="C12" t="n">
-        <v>2570.2</v>
+        <v>3350.8</v>
       </c>
       <c r="D12" t="n">
-        <v>4.94</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7314.65</v>
+        <v>6650.49</v>
       </c>
       <c r="C13" t="n">
-        <v>6574.35</v>
+        <v>5615.95</v>
       </c>
       <c r="D13" t="n">
-        <v>20.65</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60.34</v>
+        <v>52.59</v>
       </c>
       <c r="C14" t="n">
-        <v>52.07</v>
+        <v>46.7</v>
       </c>
       <c r="D14" t="n">
-        <v>8.210000000000001</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.62</v>
+        <v>10.49</v>
       </c>
       <c r="C15" t="n">
-        <v>9.960000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>15.18</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>367.35</v>
+        <v>442.23</v>
       </c>
       <c r="C16" t="n">
-        <v>342.2</v>
+        <v>376.58</v>
       </c>
       <c r="D16" t="n">
-        <v>6.41</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2293.64</v>
+        <v>1720.19</v>
       </c>
       <c r="C17" t="n">
-        <v>2105.43</v>
+        <v>1582.11</v>
       </c>
       <c r="D17" t="n">
-        <v>7.53</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>270.19</v>
+        <v>603.55</v>
       </c>
       <c r="C18" t="n">
-        <v>240.65</v>
+        <v>542.7</v>
       </c>
       <c r="D18" t="n">
-        <v>23.75</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1039.48</v>
+        <v>852.87</v>
       </c>
       <c r="C19" t="n">
-        <v>933.09</v>
+        <v>777.12</v>
       </c>
       <c r="D19" t="n">
-        <v>5.42</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9240.98</v>
+        <v>6316.38</v>
       </c>
       <c r="C20" t="n">
-        <v>8457.610000000001</v>
+        <v>5654.94</v>
       </c>
       <c r="D20" t="n">
-        <v>16.53</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2279.22</v>
+        <v>1758.33</v>
       </c>
       <c r="C21" t="n">
-        <v>2004.69</v>
+        <v>1565.28</v>
       </c>
       <c r="D21" t="n">
-        <v>9.98</v>
+        <v>7.09</v>
       </c>
     </row>
   </sheetData>
